--- a/upay/2016012301/Template_BulkAddUsers .xlsx
+++ b/upay/2016012301/Template_BulkAddUsers .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="27760" windowHeight="13060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>说明</t>
     </r>
     <r>
@@ -700,7 +707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -709,9 +716,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -1247,6 +1251,7 @@
     <col min="2" max="2" width="55.125" customWidth="1"/>
     <col min="3" max="3" width="29.1634615384615" customWidth="1"/>
     <col min="4" max="4" width="12.8461538461538" customWidth="1"/>
+    <col min="5" max="5" width="32.6826923076923" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="103" customHeight="1" spans="1:4">
@@ -1267,10 +1272,10 @@
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1278,127 +1283,127 @@
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
